--- a/public/bill_template.xlsx
+++ b/public/bill_template.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12600"/>
+    <workbookView windowWidth="29400" windowHeight="12580"/>
   </bookViews>
   <sheets>
-    <sheet name="5月" sheetId="3" r:id="rId1"/>
+    <sheet name="账单" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,8 +26,42 @@
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_7A7C75D354274AD186AF03A71950D395"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2491740" y="3733800"/>
+          <a:ext cx="1878965" cy="1469390"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>暹联出海企业管理咨询(深圳)有限公司</t>
   </si>
@@ -99,9 +133,6 @@
   </si>
   <si>
     <t>结算状态</t>
-  </si>
-  <si>
-    <t>泰铢</t>
   </si>
   <si>
     <t xml:space="preserve">如有疑问请在两个工作日之内提出反馈，以便于我们及时核实，修改账单。确认金额后请及时安排付款，以免影响贵司货物运输时效。感谢您的配合，合作愉快!
@@ -345,7 +376,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -354,150 +385,156 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -539,7 +576,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -581,10 +618,21 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -729,7 +777,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -741,34 +789,34 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -828,32 +876,32 @@
     <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -884,28 +932,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1189,53 +1240,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>43180</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>210185</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>1512570</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2491740" y="3733800"/>
-          <a:ext cx="1878965" cy="1469390"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -1773,13 +1777,8 @@
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
-      <c r="R10" s="9">
-        <f>SUM(R9:R9)</f>
-        <v>0</v>
-      </c>
-      <c r="S10" s="9" t="s">
-        <v>24</v>
-      </c>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
       <c r="T10" s="9"/>
       <c r="U10" s="9"/>
     </row>
@@ -1807,19 +1806,19 @@
       <c r="U11" s="9"/>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
@@ -1830,8 +1829,8 @@
       <c r="U12" s="9"/>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="10" t="s">
-        <v>25</v>
+      <c r="A13" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1844,7 +1843,7 @@
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
-      <c r="M13" s="9"/>
+      <c r="M13" s="10"/>
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
@@ -1867,7 +1866,7 @@
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
-      <c r="M14" s="9"/>
+      <c r="M14" s="10"/>
       <c r="N14" s="9"/>
       <c r="O14" s="9"/>
       <c r="P14" s="9"/>
@@ -1879,15 +1878,15 @@
     </row>
     <row r="15" ht="17.6" spans="1:21">
       <c r="A15" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
@@ -1908,21 +1907,24 @@
     </row>
     <row r="16" ht="128" customHeight="1" spans="1:21">
       <c r="A16" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="17"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
+      <c r="E16" s="18" t="str">
+        <f>_xlfn.DISPIMG("ID_7A7C75D354274AD186AF03A71950D395",1)</f>
+        <v>=DISPIMG("ID_7A7C75D354274AD186AF03A71950D395",1)</v>
+      </c>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
       <c r="O16" s="9"/>
@@ -1940,7 +1942,7 @@
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
-      <c r="G17" s="19"/>
+      <c r="G17" s="20"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
@@ -2026,6 +2028,5 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>